--- a/samples/tracking01/time_plots_panning_tests.xlsx
+++ b/samples/tracking01/time_plots_panning_tests.xlsx
@@ -450,7 +450,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1790749016.288087</t>
+          <t>1791281281.9022152</t>
         </is>
       </c>
     </row>
@@ -462,7 +462,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>node_3</t>
+          <t>node_4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>48</v>
+        <v>226</v>
       </c>
       <c r="E5" t="n">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F5" t="n">
         <v>150</v>
@@ -697,24 +697,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>node_4</t>
+          <t>node_5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fft_1d</t>
+          <t>ifft_1d</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FFT (1D)</t>
+          <t>IFFT (1D)</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>226</v>
+        <v>403</v>
       </c>
       <c r="E6" t="n">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="F6" t="n">
         <v>150</v>
@@ -724,381 +724,415 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>{"window": "none", "detrend": false, "log_magnitude": false}</t>
+          <t>{"length_parity": "even", "show_phase": false}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>node_5</t>
+          <t>node_6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ifft_1d</t>
+          <t>cwt_1d</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IFFT (1D)</t>
+          <t>CWT (1D)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>403</v>
+        <v>581</v>
       </c>
       <c r="E7" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F7" t="n">
         <v>150</v>
       </c>
       <c r="G7" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>{"length_parity": "even", "show_phase": false}</t>
+          <t>{"wavelet_family": "morl", "wavelet_params": {"bandwidth": 1.5, "center_freq": 1.0, "order": 2}, "scale_settings": {"scale_min": 1.0, "scale_max": 64.0, "num_scales": 40, "spacing": "log"}, "view_mode": "magnitude", "y_axis_mode": "frequency", "log_color": false, "y_log_scale": true, "colormap": "viridis"}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>node_6</t>
+          <t>node_7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>cwt_1d</t>
+          <t>image_data_simulator</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CWT (1D)</t>
+          <t>Image/Data Simulator</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>581</v>
+        <v>36</v>
       </c>
       <c r="E8" t="n">
-        <v>348</v>
+        <v>655</v>
       </c>
       <c r="F8" t="n">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="G8" t="n">
-        <v>130</v>
+        <v>270</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>{"wavelet_family": "morl", "wavelet_params": {"bandwidth": 1.5, "center_freq": 1.0, "order": 2}, "scale_settings": {"scale_min": 1.0, "scale_max": 64.0, "num_scales": 40, "spacing": "log"}, "view_mode": "magnitude", "y_axis_mode": "frequency", "log_color": false, "y_log_scale": true, "colormap": "viridis"}</t>
+          <t>{"settings": {"cameras": [{"pos": [-50, -100, 0], "view_dir": [50, 100, 0], "roll": 0.0, "hfov": 90.0, "width": 1280, "height": 960, "fps": 30.0, "start_time": 0.0, "dist": [-0.3, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]}, {"pos": [50, -100, 0], "view_dir": [-50, 100, 0], "roll": 0.0, "hfov": 90.0, "width": 1280, "height": 960, "fps": 30.0, "start_time": 0.1, "dist": [-0.3, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]}], "mesh": {"corners": [[-50.0, 0.0, -30.0], [50.0, 0.0, -30.0], [50.0, 0.0, 30.0], [-50.0, 0.0, 30.0]], "n1": 8, "n2": 5, "perspective": true, "surface_color": "#f2f2f2", "background_color": "#303030", "back_color": "#808080"}, "markers": {"type": "aruco", "size": 6.0, "aruco_dict": "DICT_4X4_250", "first_id": 0}, "speckles": {"seed": 1, "ppu": 0.0, "max_mp": 16.0, "types": [{"enabled": true, "diameter": 0.8, "density": 0.4, "color": "#000000"}, {"enabled": true, "diameter": 1.5, "density": 0.08, "color": "#000000"}, {"enabled": false, "diameter": 0.5, "density": 0.2, "color": "#404040"}, {"enabled": false, "diameter": 1.2, "density": 0.05, "color": "#808080"}]}, "motion": {"type": "rotation", "center": [0.0, 0.0, 0.0], "axis": [0.0, 0.0, 1.0], "omega": 8.0, "duration": 5.0, "sway_center": [0.0, 0.0, 0.0], "sway_axis": [0.0, -1.0, 0.0], "max_angle_deg": 5.0, "frequency_hz": 1.0}, "output": {"folder": "", "data_filename": "sim_data.npz", "image_format": "png", "filename_pattern": "cam{cam:02d}/frame_{frame:05d}", "render_images": false, "grayscale": false, "image_noise": 0.0, "point_noise": 0.0, "dropout_prob": 0.0, "nan_outside": true, "threads": 4, "seed": 12345}}}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>node_7</t>
+          <t>node_8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>image_data_simulator</t>
+          <t>mesh_scatter_viewer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Image/Data Simulator</t>
+          <t>Mesh &amp; Scatter Viewer</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>36</v>
+        <v>297</v>
       </c>
       <c r="E9" t="n">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F9" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="G9" t="n">
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>{"settings": {"cameras": [{"pos": [-50, -100, 0], "view_dir": [50, 100, 0], "roll": 0.0, "hfov": 90.0, "width": 1280, "height": 960, "fps": 30.0, "start_time": 0.0, "dist": [-0.3, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]}, {"pos": [50, -100, 0], "view_dir": [-50, 100, 0], "roll": 0.0, "hfov": 90.0, "width": 1280, "height": 960, "fps": 30.0, "start_time": 0.1, "dist": [-0.3, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]}], "mesh": {"corners": [[-50.0, 0.0, -30.0], [50.0, 0.0, -30.0], [50.0, 0.0, 30.0], [-50.0, 0.0, 30.0]], "n1": 8, "n2": 5, "perspective": true, "surface_color": "#f2f2f2", "background_color": "#303030", "back_color": "#808080"}, "markers": {"type": "aruco", "size": 6.0, "aruco_dict": "DICT_4X4_250", "first_id": 0}, "speckles": {"seed": 1, "ppu": 0.0, "max_mp": 16.0, "types": [{"enabled": true, "diameter": 0.8, "density": 0.4, "color": "#000000"}, {"enabled": true, "diameter": 1.5, "density": 0.08, "color": "#000000"}, {"enabled": false, "diameter": 0.5, "density": 0.2, "color": "#404040"}, {"enabled": false, "diameter": 1.2, "density": 0.05, "color": "#808080"}]}, "motion": {"type": "rotation", "center": [0.0, 0.0, 0.0], "axis": [0.0, 0.0, 1.0], "omega": 8.0, "duration": 5.0}, "output": {"folder": "", "data_filename": "sim_data.npz", "image_format": "png", "filename_pattern": "cam{cam:02d}/frame_{frame:05d}", "render_images": false, "grayscale": false, "image_noise": 0.0, "point_noise": 0.0, "dropout_prob": 0.0, "nan_outside": true, "threads": 4, "seed": 12345}}}</t>
+          <t>{"x": "-8:2:8", "y": "-6:2:6", "z": "", "indexing": "ij", "point_size": 2.0, "point_color": "blue", "line_width": 1.0, "line_color": "black", "marker": "o", "line_style": "solid", "show_points": true, "show_lines": true, "show_x_lines": true, "show_y_lines": true, "show_z_lines": true, "preview_enabled": true, "point_sets": [{"enabled": true, "label": "Set 1", "color": "red", "marker": "o", "size": 4.0, "text": "\n\n\n\n", "grid_lines": false, "grid_dims": "", "grid_line_color": "#aa4444", "grid_line_width": 1.0}, {"enabled": false, "label": "Set 2", "color": "blue", "marker": "s", "size": 4.0, "text": "\n\n\n\n", "grid_lines": false, "grid_dims": "", "grid_line_color": "#4444aa", "grid_line_width": 1.0}, {"enabled": false, "label": "Set 3", "color": "orange", "marker": "^", "size": 4.0, "text": "\n\n\n\n", "grid_lines": false, "grid_dims": "", "grid_line_color": "#aa8800", "grid_line_width": 1.0}, {"enabled": false, "label": "Set 4", "color": "purple", "marker": "D", "size": 4.0, "text": "\n\n\n\n", "grid_lines": false, "grid_dims": "", "grid_line_color": "#7a4499", "grid_line_width": 1.0}]}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>node_8</t>
+          <t>node_9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>mesh_scatter_viewer</t>
+          <t>structural_mesh_viewer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mesh &amp; Scatter Viewer</t>
+          <t>Structural Mesh Viewer</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>297</v>
+        <v>546</v>
       </c>
       <c r="E10" t="n">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="F10" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="G10" t="n">
         <v>220</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>{"x": "-8:2:8", "y": "-6:2:6", "z": "", "indexing": "ij", "point_size": 2.0, "point_color": "blue", "line_width": 1.0, "line_color": "black", "marker": "o", "line_style": "solid", "show_points": true, "show_lines": true, "show_x_lines": true, "show_y_lines": true, "show_z_lines": true, "preview_enabled": true, "point_sets": [{"enabled": true, "label": "Set 1", "color": "red", "marker": "o", "size": 4.0, "text": "\n\n\n\n", "grid_lines": false, "grid_dims": "", "grid_line_color": "#aa4444", "grid_line_width": 1.0}, {"enabled": false, "label": "Set 2", "color": "blue", "marker": "s", "size": 4.0, "text": "\n\n\n\n", "grid_lines": false, "grid_dims": "", "grid_line_color": "#4444aa", "grid_line_width": 1.0}, {"enabled": false, "label": "Set 3", "color": "orange", "marker": "^", "size": 4.0, "text": "\n\n\n\n", "grid_lines": false, "grid_dims": "", "grid_line_color": "#aa8800", "grid_line_width": 1.0}, {"enabled": false, "label": "Set 4", "color": "purple", "marker": "D", "size": 4.0, "text": "\n\n\n\n", "grid_lines": false, "grid_dims": "", "grid_line_color": "#7a4499", "grid_line_width": 1.0}]}</t>
+          <t>{"x_hint": "", "normal_hint": "", "view_mode": "global", "amp_x": 1.0, "amp_y": 1.0, "amp_z": 10.0, "perspective_intensity": 0.35, "show_points3d": true, "show_lines3d": true, "show_index_labels": true, "surface_field": "none", "surface_cmap": "jet", "surface_clim_auto": true, "surface_clim_min": 0.0, "surface_clim_max": 1.0, "section_axis": "axis0", "section_index": 0, "section_value": "z", "section_amp": 10.0, "section_xaxis": "index", "section_xlabel": "point index along section", "section_ylabel": "local z'", "field": "vm", "field_res": "element", "field_shading": "flat", "field_xlabel": "local x'", "field_ylabel": "local y'", "cmap": "jet", "clim_auto": true, "clim_min": 0.0, "clim_max": 1.0, "fps": 5.0, "ts_slots": [{"enabled": true, "source": "RBM Translation Z", "point_i": 0, "point_j": 0, "mode": "coord", "color": "red", "marker": "o", "marker_size": 4.0, "line_width": 1.2}, {"enabled": false, "source": "RBM Rotation X", "point_i": 0, "point_j": 0, "mode": "coord", "color": "blue", "marker": "s", "marker_size": 4.0, "line_width": 1.2}, {"enabled": false, "source": "RBM Rotation Y", "point_i": 0, "point_j": 0, "mode": "coord", "color": "green", "marker": "^", "marker_size": 4.0, "line_width": 1.2}, {"enabled": false, "source": "Local Z'", "point_i": 0, "point_j": 0, "mode": "coord", "color": "orange", "marker": "D", "marker_size": 4.0, "line_width": 1.2}, {"enabled": false, "source": "Global X", "point_i": 0, "point_j": 0, "mode": "coord", "color": "purple", "marker": "v", "marker_size": 4.0, "line_width": 1.2}, {"enabled": false, "source": "Global Y", "point_i": 0, "point_j": 0, "mode": "coord", "color": "brown", "marker": "*", "marker_size": 4.0, "line_width": 1.2}], "ts_ylim_auto": true, "ts_ylim_min": 0.0, "ts_ylim_max": 1.0, "ts_xlabel": "frame index (t)", "ts_ylabel": "value", "img_field": "vm", "img_field_res": "element", "img_shading": "flat", "img_xlabel": "image x (pixels)", "img_ylabel": "image y (pixels)", "img_cmap": "jet", "img_clim_auto": true, "img_clim_min": 0.0, "img_clim_max": 1.0, "img_alpha": 0.6, "video_quality": 95, "video_nstripes": -1}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>node_9</t>
+          <t>node_10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>structural_mesh_viewer</t>
+          <t>meshgrid</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Structural Mesh Viewer</t>
+          <t>Meshgrid</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>546</v>
+        <v>45</v>
       </c>
       <c r="E11" t="n">
-        <v>654</v>
+        <v>949</v>
       </c>
       <c r="F11" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>220</v>
+        <v>135</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>{"x_hint": "", "normal_hint": "", "view_mode": "global", "amp_x": 1.0, "amp_y": 1.0, "amp_z": 10.0, "perspective_intensity": 0.35, "show_points3d": true, "show_lines3d": true, "show_index_labels": true, "surface_field": "none", "surface_cmap": "jet", "surface_clim_auto": true, "surface_clim_min": 0.0, "surface_clim_max": 1.0, "section_axis": "axis0", "section_index": 0, "section_value": "z", "section_amp": 10.0, "section_xaxis": "index", "section_xlabel": "point index along section", "section_ylabel": "local z'", "field": "vm", "field_res": "element", "field_shading": "flat", "field_xlabel": "local x'", "field_ylabel": "local y'", "cmap": "jet", "clim_auto": true, "clim_min": 0.0, "clim_max": 1.0, "fps": 5.0, "ts_slots": [{"enabled": true, "source": "RBM Translation Z", "point_i": 0, "point_j": 0, "mode": "coord", "color": "red", "marker": "o", "marker_size": 4.0, "line_width": 1.2}, {"enabled": false, "source": "RBM Rotation X", "point_i": 0, "point_j": 0, "mode": "coord", "color": "blue", "marker": "s", "marker_size": 4.0, "line_width": 1.2}, {"enabled": false, "source": "RBM Rotation Y", "point_i": 0, "point_j": 0, "mode": "coord", "color": "green", "marker": "^", "marker_size": 4.0, "line_width": 1.2}, {"enabled": false, "source": "Local Z'", "point_i": 0, "point_j": 0, "mode": "coord", "color": "orange", "marker": "D", "marker_size": 4.0, "line_width": 1.2}, {"enabled": false, "source": "Global X", "point_i": 0, "point_j": 0, "mode": "coord", "color": "purple", "marker": "v", "marker_size": 4.0, "line_width": 1.2}, {"enabled": false, "source": "Global Y", "point_i": 0, "point_j": 0, "mode": "coord", "color": "brown", "marker": "*", "marker_size": 4.0, "line_width": 1.2}], "ts_ylim_auto": true, "ts_ylim_min": 0.0, "ts_ylim_max": 1.0, "ts_xlabel": "frame index (t)", "ts_ylabel": "value", "img_field": "vm", "img_field_res": "element", "img_shading": "flat", "img_xlabel": "image x (pixels)", "img_ylabel": "image y (pixels)", "img_cmap": "jet", "img_clim_auto": true, "img_clim_min": 0.0, "img_clim_max": 1.0, "img_alpha": 0.6, "video_quality": 95, "video_nstripes": -1}</t>
+          <t>{"x": "-8:2:8", "y": "-6:2:6", "z": "-4:2:4", "indexing": "ij", "point_size": 2.0, "point_color": "blue", "line_width": 1.0, "line_color": "black", "marker": "o", "line_style": "solid", "show_points": true, "show_lines": true, "show_x_lines": true, "show_y_lines": true, "show_z_lines": true, "preview_enabled": true}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>node_10</t>
+          <t>node_11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>meshgrid</t>
+          <t>surface_mesh_generator</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Meshgrid</t>
+          <t>Surface Mesh Generator</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>45</v>
+        <v>297</v>
       </c>
       <c r="E12" t="n">
-        <v>949</v>
+        <v>887</v>
       </c>
       <c r="F12" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="G12" t="n">
-        <v>135</v>
+        <v>230</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>{"x": "-8:2:8", "y": "-6:2:6", "z": "-4:2:4", "indexing": "ij", "point_size": 2.0, "point_color": "blue", "line_width": 1.0, "line_color": "black", "marker": "o", "line_style": "solid", "show_points": true, "show_lines": true, "show_x_lines": true, "show_y_lines": true, "show_z_lines": true, "preview_enabled": true}</t>
+          <t>{"surface_type": "plane", "points_text": "0 0 0\n1 1 1\n2 2 2\n3 3 3\n\n", "origin_idx": 0, "xaxis_idx": 1, "yside_idx": -1, "axis_hint": ["0", "0", "1"], "legacy_height_idx": null, "theta_unit": "degrees", "reverse_theta": false, "a1_start": 0.0, "a1_end": 1.0, "a1_count": 2000, "a2_start": 0.0, "a2_end": 1.0, "a2_count": 2000, "dtype": "float64", "mem_override": false, "mdraw": 20, "ndraw": 20, "perspective_intensity": 0.35, "given_marker": "o", "given_size": 5.0, "given_color": "red", "surf_marker": "+", "surf_size": 2.5, "surf_color": "blue", "surf_lines": true, "surf_line_color": "#88aacc"}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>node_11</t>
+          <t>node_12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>surface_mesh_generator</t>
+          <t>scatter_plot</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Surface Mesh Generator</t>
+          <t>2D Scatter Plot</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>297</v>
+        <v>702</v>
       </c>
       <c r="E13" t="n">
-        <v>887</v>
+        <v>69</v>
       </c>
       <c r="F13" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="G13" t="n">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>{"surface_type": "plane", "points_text": "0 0 0\n1 1 1\n2 2 2\n3 3 3\n\n", "origin_idx": 0, "xaxis_idx": 1, "yside_idx": -1, "axis_hint": ["0", "0", "1"], "legacy_height_idx": null, "theta_unit": "degrees", "reverse_theta": false, "a1_start": 0.0, "a1_end": 1.0, "a1_count": 2000, "a2_start": 0.0, "a2_end": 1.0, "a2_count": 2000, "dtype": "float64", "mem_override": false, "mdraw": 20, "ndraw": 20, "perspective_intensity": 0.35, "given_marker": "o", "given_size": 5.0, "given_color": "red", "surf_marker": "+", "surf_size": 2.5, "surf_color": "blue", "surf_lines": true, "surf_line_color": "#88aacc"}</t>
+          <t>{"xlabel": "x", "ylabel": "y", "title": "", "grid_on": true, "grid_style": "--", "grid_color": "gray", "legend_on": true, "legend_loc": "best", "xscale": "linear", "yscale": "linear", "curves": [{"enabled": true, "legend": "Curve 1", "marker": "o", "marker_size": 6.0, "marker_color": "red", "line_width": 1.5, "line_style": "-", "line_color": "red", "source": "text", "x_expr": "c1[:,0]", "y_expr": "c1[:,1]", "text": "2 2\n2 2\n3 1\n2 -1\n0 -1\n-1 0\n"}, {"enabled": false, "legend": "Curve 2", "marker": "s", "marker_size": 6.0, "marker_color": "blue", "line_width": 1.5, "line_style": "-", "line_color": "blue", "source": "pin", "x_expr": "c2[:,0]", "y_expr": "c2[:,1]", "text": "0 0\n1 1\n2 0\n1 -1\n0 -1\n-1 0\n0 0\n1 1\n2 0\n1 -1\n0 -1\n-1 0\n0 0\n1 1\n2 0\n1 -1\n0 -1\n-1 0\n0 0\n1 1\n2 0\n1 -1\n0 -1\n-1 0\n"}, {"enabled": false, "legend": "Curve 3", "marker": "^", "marker_size": 6.0, "marker_color": "green", "line_width": 1.5, "line_style": "-", "line_color": "green", "source": "pin", "x_expr": "c3[:,0]", "y_expr": "c3[:,1]", "text": "0 0\n1 1\n2 0\n1 -1\n0 -1\n-1 0\n0 0\n1 1\n2 0\n1 -1\n0 -1\n-1 0\n0 0\n1 1\n2 0\n1 -1\n0 -1\n-1 0\n0 0\n1 1\n2 0\n1 -1\n0 -1\n-1 0\n"}, {"enabled": false, "legend": "Curve 4", "marker": "D", "marker_size": 6.0, "marker_color": "orange", "line_width": 1.5, "line_style": "-", "line_color": "orange", "source": "pin", "x_expr": "c4[:,0]", "y_expr": "c4[:,1]", "text": "0 0\n1 1\n2 0\n1 -1\n0 -1\n-1 0\n0 0\n1 1\n2 0\n1 -1\n0 -1\n-1 0\n0 0\n1 1\n2 0\n1 -1\n0 -1\n-1 0\n0 0\n1 1\n2 0\n1 -1\n0 -1\n-1 0\n"}]}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>node_12</t>
+          <t>node_13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>scatter_plot</t>
+          <t>generic_display</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2D Scatter Plot</t>
+          <t>Generic Display</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>702</v>
+        <v>788</v>
       </c>
       <c r="E14" t="n">
-        <v>69</v>
+        <v>283</v>
       </c>
       <c r="F14" t="n">
         <v>210</v>
       </c>
       <c r="G14" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>{"xlabel": "x", "ylabel": "y", "title": "", "grid_on": true, "grid_style": "--", "grid_color": "gray", "legend_on": true, "legend_loc": "best", "xscale": "linear", "yscale": "linear", "curves": [{"enabled": true, "legend": "Curve 1", "marker": "o", "marker_size": 6.0, "marker_color": "red", "line_width": 1.5, "line_style": "-", "line_color": "red", "source": "text", "x_expr": "c1[:,0]", "y_expr": "c1[:,1]", "text": "2 2\n2 2\n3 1\n2 -1\n0 -1\n-1 0\n"}, {"enabled": false, "legend": "Curve 2", "marker": "s", "marker_size": 6.0, "marker_color": "blue", "line_width": 1.5, "line_style": "-", "line_color": "blue", "source": "pin", "x_expr": "c2[:,0]", "y_expr": "c2[:,1]", "text": "0 0\n1 1\n2 0\n1 -1\n0 -1\n-1 0\n0 0\n1 1\n2 0\n1 -1\n0 -1\n-1 0\n0 0\n1 1\n2 0\n1 -1\n0 -1\n-1 0\n0 0\n1 1\n2 0\n1 -1\n0 -1\n-1 0\n"}, {"enabled": false, "legend": "Curve 3", "marker": "^", "marker_size": 6.0, "marker_color": "green", "line_width": 1.5, "line_style": "-", "line_color": "green", "source": "pin", "x_expr": "c3[:,0]", "y_expr": "c3[:,1]", "text": "0 0\n1 1\n2 0\n1 -1\n0 -1\n-1 0\n0 0\n1 1\n2 0\n1 -1\n0 -1\n-1 0\n0 0\n1 1\n2 0\n1 -1\n0 -1\n-1 0\n0 0\n1 1\n2 0\n1 -1\n0 -1\n-1 0\n"}, {"enabled": false, "legend": "Curve 4", "marker": "D", "marker_size": 6.0, "marker_color": "orange", "line_width": 1.5, "line_style": "-", "line_color": "orange", "source": "pin", "x_expr": "c4[:,0]", "y_expr": "c4[:,1]", "text": "0 0\n1 1\n2 0\n1 -1\n0 -1\n-1 0\n0 0\n1 1\n2 0\n1 -1\n0 -1\n-1 0\n0 0\n1 1\n2 0\n1 -1\n0 -1\n-1 0\n0 0\n1 1\n2 0\n1 -1\n0 -1\n-1 0\n"}]}</t>
+          <t>{"expr": "{'aa':x, 'bb':x.T@x}"}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>node_13</t>
+          <t>node_14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>generic_display</t>
+          <t>array_input</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Generic Display</t>
+          <t>Array Input</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>788</v>
+        <v>471</v>
       </c>
       <c r="E15" t="n">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="F15" t="n">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="G15" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>{"expr": "{'aa':x, 'bb':x.T@x}"}</t>
+          <t>{"csv": "1, 2, 3\n4, 5, 6", "dtype": "float64", "shape_mode": "auto", "shape_text": ""}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>node_14</t>
+          <t>node_15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>array_input</t>
+          <t>generic_display</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Array Input</t>
+          <t>Generic Display</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>471</v>
+        <v>1061</v>
       </c>
       <c r="E16" t="n">
-        <v>242</v>
+        <v>380</v>
       </c>
       <c r="F16" t="n">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="G16" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>{"csv": "1, 2, 3\n4, 5, 6", "dtype": "float64", "shape_mode": "auto", "shape_text": ""}</t>
+          <t>{"expr": ""}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>node_15</t>
+          <t>node_16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>generic_display</t>
+          <t>bandpass_filter</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Generic Display</t>
+          <t>Band-Pass Filter</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1061</v>
+        <v>33</v>
       </c>
       <c r="E17" t="n">
-        <v>380</v>
+        <v>337</v>
       </c>
       <c r="F17" t="n">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="G17" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>{"expr": ""}</t>
+          <t>{"filter": {"mode": "bandpass", "f_low": 0.5, "f_high": 5.0, "order": 4.0, "shape": "butterworth", "remove_mean": true, "pad_frac": 0.1}, "signal_index": 0, "show_db": false}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>node_17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>signal_generator</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Signal Generator</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11</v>
+      </c>
+      <c r="E18" t="n">
+        <v>211</v>
+      </c>
+      <c r="F18" t="n">
+        <v>150</v>
+      </c>
+      <c r="G18" t="n">
+        <v>110</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>{"common": {"duration": 10.0, "dt": 0.01}, "sine_channels": [{"enabled": true, "amplitude": 1.0, "frequency": 1.0, "decay": 0.0, "time_shift": 0.0}, {"enabled": false, "amplitude": 1.0, "frequency": 2.0, "decay": 0.0, "time_shift": 0.0}, {"enabled": false, "amplitude": 1.0, "frequency": 3.0, "decay": 0.0, "time_shift": 0.0}, {"enabled": false, "amplitude": 1.0, "frequency": 4.0, "decay": 0.0, "time_shift": 0.0}, {"enabled": false, "amplitude": 1.0, "frequency": 5.0, "decay": 0.0, "time_shift": 0.0}, {"enabled": false, "amplitude": 1.0, "frequency": 6.0, "decay": 0.0, "time_shift": 0.0}], "noise_channel": {"enabled": false, "distribution": "gaussian", "amplitude": 0.05, "seed": 0}}</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1137,6 +1171,11 @@
           <t>dst_pin</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>geometry_json</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1159,6 +1198,11 @@
           <t>x</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>{"h1": [42.0, -2.0], "h2": [-37.0, -3.0], "mid": [0.509, -0.018]}</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1181,6 +1225,7 @@
           <t>x</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
